--- a/data/b2_primavera/B2 Primavera 05-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 05-2026.xlsx
@@ -4891,43 +4891,43 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1805.6</v>
+        <v>1707.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>56938.01</v>
+        <v>1048.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>4140.46</v>
+        <v>57314.49</v>
       </c>
     </row>
     <row r="5">
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3841.05</v>
+        <v>4101.47</v>
       </c>
     </row>
     <row r="8">
@@ -4990,52 +4990,52 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>738.6900000000001</v>
+        <v>1033.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1144.62</v>
+        <v>1242.65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1843.02</v>
+        <v>8118.08</v>
       </c>
     </row>
     <row r="11">
@@ -5044,16 +5044,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>8548.719999999999</v>
+        <v>1622.04</v>
       </c>
     </row>
     <row r="12">
@@ -5062,16 +5062,16 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1688.6</v>
+        <v>1318.17</v>
       </c>
     </row>
     <row r="13">
@@ -5089,48 +5089,48 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3878.89</v>
+        <v>3683.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>985.42</v>
+        <v>20281.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>20197.28</v>
+        <v>2518.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -5139,11 +5139,11 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1903.29</v>
+        <v>2038.84</v>
       </c>
     </row>
     <row r="17">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>4034.11</v>
+        <v>3829.2</v>
       </c>
     </row>
     <row r="18">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>4098.76</v>
+        <v>3879.55</v>
       </c>
     </row>
   </sheetData>
